--- a/DataTables/Datas/battle.deck.xlsx
+++ b/DataTables/Datas/battle.deck.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F40629-3B00-4AF6-A813-62B1A9881EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB28621F-B608-47DA-A96F-250BDE91B70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="0" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>##var</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>3002,3002,3002,3002,3002,3003,3003,3003,3003,3004</t>
   </si>
 </sst>
 </file>
@@ -100,8 +103,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -468,8 +474,8 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5">
-        <v>3001</v>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/battle.deck.xlsx
+++ b/DataTables/Datas/battle.deck.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB28621F-B608-47DA-A96F-250BDE91B70E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A3B544-BBD6-4A3A-9FCF-6A52D86FEB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,13 +80,57 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF365F91"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F9F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF9EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -103,11 +147,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -429,52 +488,52 @@
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="5">
         <v>1001</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
     </row>
